--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Buku Kerawanan SJB 2026 Sec 2.10 (Gambar 2.9 -- 2 halaman SLD -- + Tabel 2.8)</t>
+          <t>Buku Kerawanan SJB 2026 Sec 2.10 (Gambar 2.9 PDF98, tiga panel; Tabel 2.8); koreksi Angke-Ancol pengguna 2026-09-12</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,15 +549,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sisi Priok &amp; Cawang Baru</t>
+          <t>Sisi Priok</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PRTRU;PRTMR;PRBRT;MKLMA;CWBRU</t>
+          <t>PRTRU;PRTMR;PRBRT;MKLMA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sisi Cawang Baru</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CWBRU</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>82</v>
       </c>
     </row>
@@ -572,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,57 +633,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -700,24 +735,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -756,24 +792,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -811,39 +848,40 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>BKASI</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2 IBT (unit 2,4)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -881,39 +919,40 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>MTWAR</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -952,24 +991,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1008,24 +1048,25 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1064,26 +1105,27 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1162,25 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1176,28 +1219,29 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1236,28 +1280,29 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1296,26 +1341,27 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -1352,26 +1398,27 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -1408,24 +1455,25 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1464,24 +1512,25 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1520,24 +1569,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1576,24 +1626,25 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -1632,26 +1683,27 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -1687,35 +1739,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
         <is>
           <t>CWBRU</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -1752,26 +1805,27 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -1808,28 +1862,29 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R21" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -1868,28 +1923,29 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -1928,24 +1984,25 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -1984,28 +2041,29 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>1;6</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2044,28 +2102,29 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R25" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2104,28 +2163,29 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R26" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2164,24 +2224,25 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2220,28 +2281,29 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2;6</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2280,28 +2342,29 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2340,24 +2403,25 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2396,24 +2460,25 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2452,28 +2517,29 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2512,28 +2578,29 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2572,24 +2639,25 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2628,24 +2696,25 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2684,26 +2753,27 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -2740,24 +2810,25 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2796,24 +2867,25 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2852,24 +2924,25 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2908,24 +2981,25 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -2964,24 +3038,25 @@
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -3020,24 +3095,25 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -3076,24 +3152,25 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -3132,24 +3209,25 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -3188,26 +3266,27 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3244,28 +3323,29 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>3;7</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R46" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -3304,30 +3384,31 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3364,26 +3445,27 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3420,26 +3502,27 @@
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3476,26 +3559,27 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3532,30 +3616,31 @@
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3592,26 +3677,27 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3648,26 +3734,27 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3704,26 +3791,161 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>MTWAR</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3887,7 +4109,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4369,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4432,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>BEKASI;PRIOK</t>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5968,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6539,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>PRIOK;CAWANG</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6665,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6799,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>PRIOK;CAWANG</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6862,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6925,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6988,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6833,7 +7055,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG;PRIOK</t>
         </is>
       </c>
     </row>
@@ -6900,7 +7122,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -6963,7 +7185,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>PRIOK;CAWANG</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7248,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7311,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7374,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7437,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7500,259 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SUTT Angke - Ancol</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ANGKE</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ANCOL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
           <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SKTT Marunda - Kelapa Baru (lanjutan antar panel)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MRNDA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>KLBRU</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>BEKASI;PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUTT Harapan Indah - Plumpang 40 KA (lanjutan)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HNDAH</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>BEKASI;PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SUTT Kandang Sapi - Plumpang 40 KA (lanjutan)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>KDSPI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>BEKASI;PRIOK</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7376,7 +7850,11 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -7411,7 +7889,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7446,7 +7928,11 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -7481,7 +7967,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7516,7 +8006,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7551,7 +8045,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7586,7 +8084,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7621,7 +8123,11 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7656,7 +8162,11 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7691,7 +8201,596 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PGSAN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PGSAN (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PLMAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PLMAS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PLMAS (lanjutan panel CAWANG)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PGSAN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MGBSR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MGBSR (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MGRAI</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MGRAI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MGRAI (lanjutan panel CAWANG)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MGBSR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MGRAI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MGRAI (lanjutan panel CAWANG)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GDPLA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GDPLA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GDPLA (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MGRAI</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GDPLA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GDPLA (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GMLMA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GMLMA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GMLMA (lanjutan panel CAWANG)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GDPLA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MRNDA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MRNDA (lanjutan panel BEKASI)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>KLBRU</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KLBRU</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>KLBRU (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MRNDA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HNDAH</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HNDAH (lanjutan panel BEKASI)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PLPNG40 (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HNDAH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KDSPI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>KDSPI (lanjutan panel BEKASI)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PRIOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PLPNG40</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PLPNG40 (lanjutan panel PRIOK)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KDSPI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CWANG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cawang (lanjutan)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>STBDI</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -845,7 +845,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>

--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -7767,7 +7767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7793,25 +7793,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -7836,21 +7841,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -7875,21 +7881,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -7914,21 +7921,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -7953,21 +7961,22 @@
           <t>PGDNGK</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -7992,21 +8001,22 @@
           <t>PGSAN</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8031,21 +8041,22 @@
           <t>PGSAN</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8070,21 +8081,22 @@
           <t>PKRNG</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8109,21 +8121,22 @@
           <t>ANGKE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8148,21 +8161,22 @@
           <t>ANGKE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8187,21 +8201,22 @@
           <t>ANGKE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8226,21 +8241,22 @@
           <t>PLMAS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>CAWANG</t>
         </is>
@@ -8265,21 +8281,22 @@
           <t>PGSAN</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8304,21 +8321,22 @@
           <t>MGRAI</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
         <is>
           <t>CAWANG</t>
         </is>
@@ -8343,21 +8361,22 @@
           <t>MGBSR</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8382,21 +8401,22 @@
           <t>GDPLA</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8421,21 +8441,22 @@
           <t>MGRAI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>CAWANG</t>
         </is>
@@ -8460,21 +8481,22 @@
           <t>GMLMA</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
         <is>
           <t>CAWANG</t>
         </is>
@@ -8499,21 +8521,22 @@
           <t>GDPLA</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8538,21 +8561,22 @@
           <t>KLBRU</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8577,21 +8601,22 @@
           <t>MRNDA</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -8616,21 +8641,22 @@
           <t>PLPNG40</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8655,21 +8681,22 @@
           <t>HNDAH</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -8694,21 +8721,22 @@
           <t>PLPNG40</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
         <is>
           <t>PRIOK</t>
         </is>
@@ -8733,21 +8761,22 @@
           <t>KDSPI</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
@@ -8772,21 +8801,22 @@
           <t>STBDI</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
         <is>
           <t>CAWANG</t>
         </is>

--- a/samples/ss_prbc_ingest.xlsx
+++ b/samples/ss_prbc_ingest.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,7 +822,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 2,4 Bekasi</t>
+          <t>IBT 2 Bekasi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -858,11 +858,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 2,4)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -893,12 +889,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2 Muaratawar</t>
+          <t>IBT 4 Bekasi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1 MTWAR</t>
+          <t>IBT 4 BKASI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -916,24 +912,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>BKASI</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -964,31 +956,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bekasi (bus 150 kV)</t>
+          <t>IBT 1 Muaratawar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>IBT 1 MTWAR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MTWAR</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1021,31 +1023,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Muaratawar (bus 150 kV)</t>
+          <t>IBT 2 Muaratawar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>MTWAR</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1078,12 +1090,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Marunda</t>
+          <t>Bekasi (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MRNDA</t>
+          <t>BKASI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1092,7 +1104,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1135,12 +1147,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pegangsaan Dua</t>
+          <t>Muaratawar (bus 150 kV)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PGDRU</t>
+          <t>MTWAR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1149,7 +1161,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1192,12 +1204,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rawa Terate</t>
+          <t>Marunda</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RATER</t>
+          <t>MRNDA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1228,14 +1240,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1253,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Penggilingan</t>
+          <t>Pegangsaan Dua</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PGLNG</t>
+          <t>PGDRU</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1289,14 +1297,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1314,12 +1318,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Harapan Indah</t>
+          <t>Rawa Terate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HNDAH</t>
+          <t>RATER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1350,10 +1354,14 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1371,12 +1379,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kandang Sapi</t>
+          <t>Penggilingan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KDSPI</t>
+          <t>PGLNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1407,10 +1415,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1428,12 +1440,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pegangsaan Konv</t>
+          <t>Harapan Indah</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PGDNGK</t>
+          <t>HNDAH</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1442,7 +1454,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1485,12 +1497,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rawa Makmur</t>
+          <t>Kandang Sapi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RAWAM</t>
+          <t>KDSPI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1499,7 +1511,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1542,12 +1554,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rawa Kucing</t>
+          <t>Pegangsaan Konv</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAKUN</t>
+          <t>PGDNGK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1599,12 +1611,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JGC</t>
+          <t>Rawa Makmur</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JGC</t>
+          <t>RAWAM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1656,25 +1668,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GITET Cawang Baru</t>
+          <t>Rawa Kucing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CWBRU</t>
+          <t>RAKUN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1703,7 +1715,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CAWANG</t>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -1713,38 +1725,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IBT 1 Cawang Baru</t>
+          <t>JGC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IBT 1 CWBRU</t>
+          <t>JGC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CWBRU</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1768,7 +1772,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CAWANG</t>
+          <t>BEKASI</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1782,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cawang Baru (bus 150 kV)</t>
+          <t>GITET Cawang Baru</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1788,7 +1792,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1796,7 +1800,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>500 kV</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1835,30 +1839,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PLTGU Priok Blok 3</t>
+          <t>IBT 1 Cawang Baru</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KIT_PRIOK_B3</t>
+          <t>IBT 1 CWBRU</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CWBRU</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1871,14 +1883,10 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1886,7 +1894,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -1896,17 +1904,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PLTGU Priok Blok 1 &amp; 2</t>
+          <t>Cawang Baru (bus 150 kV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KIT_PRIOK_B12</t>
+          <t>CWBRU</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1932,14 +1940,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1947,7 +1951,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PLTGU Muarakarang ST 3.0</t>
+          <t>PLTGU Priok Blok 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KIT_MKR_ST30</t>
+          <t>KIT_PRIOK_B3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1993,10 +1997,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2014,17 +2022,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Priok Timur Lama</t>
+          <t>PLTGU Priok Blok 1 &amp; 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PRTRU</t>
+          <t>KIT_PRIOK_B12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2055,7 +2063,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1;6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2075,17 +2083,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Priok Timur Baru</t>
+          <t>PLTGU Muarakarang ST 3.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRTMR</t>
+          <t>KIT_MKR_ST30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2111,14 +2119,10 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2136,12 +2140,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Priok Barat</t>
+          <t>Priok Timur Lama</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PRBRT</t>
+          <t>PRTRU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2177,7 +2181,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1;6</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2197,17 +2201,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Muarakarang Lama</t>
+          <t>Priok Timur Baru</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MKLMA</t>
+          <t>PRTMR</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2233,10 +2237,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2254,21 +2262,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plumpang (40 KA)</t>
+          <t>Priok Barat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PLPNG40</t>
+          <t>PRBRT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2295,7 +2303,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2;6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2315,12 +2323,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Plumpang (20 KA)</t>
+          <t>Muarakarang Lama</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PLPNG20</t>
+          <t>MKLMA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2329,7 +2337,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2351,14 +2359,10 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2376,12 +2380,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ancol</t>
+          <t>Plumpang (40 KA)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ANCOL</t>
+          <t>PLPNG40</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2412,10 +2416,14 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2;6</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2433,12 +2441,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemayoran</t>
+          <t>Plumpang (20 KA)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KMYRN</t>
+          <t>PLPNG20</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2469,10 +2477,14 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2490,12 +2502,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pulo Gadung Baru</t>
+          <t>Ancol</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PLPRU</t>
+          <t>ANCOL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2526,14 +2538,10 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2551,12 +2559,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pegangsaan</t>
+          <t>Kemayoran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PGSAN</t>
+          <t>KMYRN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2587,14 +2595,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2612,12 +2616,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pulo Mas Indo (KTT)</t>
+          <t>Pulo Gadung Baru</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PLNDO</t>
+          <t>PLPRU</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2648,10 +2652,14 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2669,12 +2677,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Angke</t>
+          <t>Pegangsaan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ANGKE</t>
+          <t>PGSAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2705,10 +2713,14 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -2726,12 +2738,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cinang / Cawang Baru bawah</t>
+          <t>Pulo Mas Indo (KTT)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CNANG</t>
+          <t>PLNDO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2756,7 +2768,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Milik Pelanggan</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
@@ -2773,7 +2785,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>CAWANG</t>
+          <t>PRIOK</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2795,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kelapa Gading</t>
+          <t>Angke</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KLPGD</t>
+          <t>ANGKE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2797,7 +2809,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2840,12 +2852,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pekayon Raya</t>
+          <t>Cinang / Cawang Baru bawah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PKRNG</t>
+          <t>CNANG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2854,7 +2866,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2887,7 +2899,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>PRIOK</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -2897,17 +2909,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gambir Baru</t>
+          <t>Kelapa Gading</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GMBRU</t>
+          <t>KLPGD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -2954,12 +2966,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sunter</t>
+          <t>Pekayon Raya</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SNTER</t>
+          <t>PKRNG</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3011,12 +3023,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gunung Sahari</t>
+          <t>Gambir Baru</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GNSHR</t>
+          <t>GMBRU</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3068,12 +3080,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pademangan</t>
+          <t>Sunter</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PDMGN</t>
+          <t>SNTER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3125,12 +3137,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Menteng Besar</t>
+          <t>Gunung Sahari</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MGBSR</t>
+          <t>GNSHR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3182,12 +3194,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kelapa Baru (KTT)</t>
+          <t>Pademangan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KLBRU</t>
+          <t>PDMGN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3239,17 +3251,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pulo Mas</t>
+          <t>Menteng Besar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PLMAS</t>
+          <t>MGBSR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3286,7 +3298,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>CAWANG</t>
+          <t>PRIOK</t>
         </is>
       </c>
     </row>
@@ -3296,21 +3308,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GIS Gedung Pola</t>
+          <t>Kelapa Baru (KTT)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GDPLA</t>
+          <t>KLBRU</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3326,20 +3338,16 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Milik Pelanggan</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>3;7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3357,21 +3365,21 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GIS Manggarai</t>
+          <t>Pulo Mas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MGRAI</t>
+          <t>PLMAS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3393,14 +3401,10 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3418,17 +3422,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cempaka Putih</t>
+          <t>GIS Gedung Pola</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CMPTH</t>
+          <t>GDPLA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3454,10 +3458,14 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>3;7</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3465,7 +3473,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CAWANG</t>
+          <t>PRIOK</t>
         </is>
       </c>
     </row>
@@ -3475,17 +3483,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tomang Tinggi</t>
+          <t>GIS Manggarai</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TMTGI</t>
+          <t>MGRAI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3511,10 +3519,14 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3532,21 +3544,21 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gambir Lama</t>
+          <t>Cempaka Putih</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GMLMA</t>
+          <t>CMPTH</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3589,21 +3601,21 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GIS Dukuh Atas</t>
+          <t>Tomang Tinggi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DKTAS</t>
+          <t>TMTGI</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3625,14 +3637,10 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3650,12 +3658,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GIS Kebon Sirih</t>
+          <t>Gambir Lama</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KBSRH</t>
+          <t>GMLMA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3664,7 +3672,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3707,21 +3715,21 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Setiabudi</t>
+          <t>GIS Dukuh Atas</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>STBDI</t>
+          <t>DKTAS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3743,10 +3751,14 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -3764,17 +3776,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cawang Lama</t>
+          <t>GIS Kebon Sirih</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>KBSRH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3821,41 +3833,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IBT 4 BKASI</t>
+          <t>Setiabudi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IBT 4 BKASI</t>
+          <t>STBDI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>BKASI</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -3878,7 +3880,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>BEKASI</t>
+          <t>CAWANG</t>
         </is>
       </c>
     </row>
@@ -3888,41 +3890,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IBT 2 MTWAR</t>
+          <t>Cawang Lama</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IBT 2 MTWAR</t>
+          <t>CWANG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>MTWAR</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3944,6 +3936,140 @@
         </is>
       </c>
       <c r="S56" t="inlineStr">
+        <is>
+          <t>CAWANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IBT 4 BKASI</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>BKASI</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>BEKASI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IBT 2 MTWAR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>MTWAR</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>BEKASI</t>
         </is>
